--- a/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263240723766579</v>
+        <v>1.266667023254401</v>
       </c>
       <c r="C3" t="n">
-        <v>4.675963086374182</v>
+        <v>4.642829101355852</v>
       </c>
       <c r="D3" t="n">
-        <v>6.042230153322411</v>
+        <v>6.042573765018897</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98143396346317</v>
+        <v>11.95206988962915</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.400414877577397</v>
+        <v>1.403767680958917</v>
       </c>
       <c r="C4" t="n">
-        <v>5.263233087549997</v>
+        <v>5.172791441909146</v>
       </c>
       <c r="D4" t="n">
-        <v>6.272047769971824</v>
+        <v>6.235134649669795</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93569573509922</v>
+        <v>12.81169377253786</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.58470417184801</v>
+        <v>1.582671873581764</v>
       </c>
       <c r="C5" t="n">
-        <v>6.073897362534513</v>
+        <v>5.866725929229537</v>
       </c>
       <c r="D5" t="n">
-        <v>6.491432372460141</v>
+        <v>6.479284519442127</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15003390684267</v>
+        <v>13.92868232225343</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.792621593634852</v>
+        <v>1.779354826838336</v>
       </c>
       <c r="C6" t="n">
-        <v>7.052715585122976</v>
+        <v>6.702012874266546</v>
       </c>
       <c r="D6" t="n">
-        <v>6.707548049975878</v>
+        <v>6.799845531576416</v>
       </c>
       <c r="E6" t="n">
-        <v>15.55288522873371</v>
+        <v>15.2812132326813</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.023157643559778</v>
+        <v>1.994675140772877</v>
       </c>
       <c r="C7" t="n">
-        <v>8.212571955448183</v>
+        <v>7.672100239348088</v>
       </c>
       <c r="D7" t="n">
-        <v>6.981705819428913</v>
+        <v>7.187625303230602</v>
       </c>
       <c r="E7" t="n">
-        <v>17.21743541843687</v>
+        <v>16.85440068335157</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.235834757966034</v>
+        <v>1.213903682561419</v>
       </c>
       <c r="C8" t="n">
-        <v>5.85232091552748</v>
+        <v>5.350226822557421</v>
       </c>
       <c r="D8" t="n">
-        <v>5.147935794940078</v>
+        <v>5.427743473471914</v>
       </c>
       <c r="E8" t="n">
-        <v>12.23609146843359</v>
+        <v>11.99187397859076</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.542788496144355</v>
+        <v>1.523100227117996</v>
       </c>
       <c r="C9" t="n">
-        <v>7.307129878997046</v>
+        <v>6.628375604909048</v>
       </c>
       <c r="D9" t="n">
-        <v>5.476270761988023</v>
+        <v>5.974921444474854</v>
       </c>
       <c r="E9" t="n">
-        <v>14.32618913712943</v>
+        <v>14.1263972765019</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.865255676533022</v>
+        <v>1.850230348576745</v>
       </c>
       <c r="C10" t="n">
-        <v>8.954644113658773</v>
+        <v>8.12644893589405</v>
       </c>
       <c r="D10" t="n">
-        <v>5.876861630864243</v>
+        <v>6.512353846503999</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69676142105604</v>
+        <v>16.48903313097479</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.186426631024922</v>
+        <v>2.186765058736039</v>
       </c>
       <c r="C11" t="n">
-        <v>10.69839437657805</v>
+        <v>9.802203334398461</v>
       </c>
       <c r="D11" t="n">
-        <v>6.235556679897509</v>
+        <v>7.014492287202731</v>
       </c>
       <c r="E11" t="n">
-        <v>19.12037768750049</v>
+        <v>19.00346068033723</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.510884287259505</v>
+        <v>2.510841207555312</v>
       </c>
       <c r="C12" t="n">
-        <v>12.61147953372704</v>
+        <v>11.56016176923857</v>
       </c>
       <c r="D12" t="n">
-        <v>6.573196229844489</v>
+        <v>7.506526214594225</v>
       </c>
       <c r="E12" t="n">
-        <v>21.69556005083103</v>
+        <v>21.5775291913881</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.812259721911054</v>
+        <v>2.812276407568979</v>
       </c>
       <c r="C13" t="n">
-        <v>14.52926431992755</v>
+        <v>13.37632273746454</v>
       </c>
       <c r="D13" t="n">
-        <v>6.946483791346208</v>
+        <v>8.042416262124863</v>
       </c>
       <c r="E13" t="n">
-        <v>24.28800783318481</v>
+        <v>24.23101540715839</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.620374585859361</v>
+        <v>1.61221626243707</v>
       </c>
       <c r="C14" t="n">
-        <v>10.16681232807024</v>
+        <v>9.364665548838348</v>
       </c>
       <c r="D14" t="n">
-        <v>5.306061634619779</v>
+        <v>6.153653515081261</v>
       </c>
       <c r="E14" t="n">
-        <v>17.09324854854938</v>
+        <v>17.13053532635668</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.645811668876396</v>
+        <v>1.636887582244792</v>
       </c>
       <c r="C15" t="n">
-        <v>11.11564203179366</v>
+        <v>10.26347520703039</v>
       </c>
       <c r="D15" t="n">
-        <v>5.218980613253086</v>
+        <v>6.18832884399526</v>
       </c>
       <c r="E15" t="n">
-        <v>17.98043431392314</v>
+        <v>18.08869163327044</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.895263943048468</v>
+        <v>1.877307777537793</v>
       </c>
       <c r="C16" t="n">
-        <v>13.24236281359536</v>
+        <v>12.20788544015345</v>
       </c>
       <c r="D16" t="n">
-        <v>5.546629092068417</v>
+        <v>6.654374296678264</v>
       </c>
       <c r="E16" t="n">
-        <v>20.68425584871224</v>
+        <v>20.7395675143695</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.508376807758885</v>
+        <v>1.490656261697229</v>
       </c>
       <c r="C17" t="n">
-        <v>12.23176154432073</v>
+        <v>11.30484444935611</v>
       </c>
       <c r="D17" t="n">
-        <v>5.064924763502677</v>
+        <v>6.190606498669113</v>
       </c>
       <c r="E17" t="n">
-        <v>18.80506311558229</v>
+        <v>18.98610720972245</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.714131491614931</v>
+        <v>1.678386057703305</v>
       </c>
       <c r="C18" t="n">
-        <v>14.32565268289241</v>
+        <v>13.18171044042699</v>
       </c>
       <c r="D18" t="n">
-        <v>5.380527197986899</v>
+        <v>6.582716531745289</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42031137249424</v>
+        <v>21.44281302987558</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.708633704471149</v>
+        <v>1.664612137412722</v>
       </c>
       <c r="C19" t="n">
-        <v>15.36267278288832</v>
+        <v>14.09132914084278</v>
       </c>
       <c r="D19" t="n">
-        <v>5.39250451997871</v>
+        <v>6.661442880148839</v>
       </c>
       <c r="E19" t="n">
-        <v>22.46381100733818</v>
+        <v>22.41738415840435</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.90231289156496</v>
+        <v>1.831892128739336</v>
       </c>
       <c r="C20" t="n">
-        <v>17.57693600747771</v>
+        <v>16.06182441046769</v>
       </c>
       <c r="D20" t="n">
-        <v>5.662887655205325</v>
+        <v>7.076584714366647</v>
       </c>
       <c r="E20" t="n">
-        <v>25.14213655424799</v>
+        <v>24.97030125357367</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.133368819690688</v>
+        <v>1.07812587637272</v>
       </c>
       <c r="C21" t="n">
-        <v>12.82904703010745</v>
+        <v>11.66603924722555</v>
       </c>
       <c r="D21" t="n">
-        <v>4.673933922809342</v>
+        <v>5.907843524891946</v>
       </c>
       <c r="E21" t="n">
-        <v>18.63634977260748</v>
+        <v>18.65200864849022</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266667023254401</v>
+        <v>1.264035939407019</v>
       </c>
       <c r="C3" t="n">
-        <v>4.642829101355852</v>
+        <v>4.644635517131666</v>
       </c>
       <c r="D3" t="n">
-        <v>6.042573765018897</v>
+        <v>6.156377958895187</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95206988962915</v>
+        <v>12.06504941543387</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.403767680958917</v>
+        <v>1.398898476111962</v>
       </c>
       <c r="C4" t="n">
-        <v>5.172791441909146</v>
+        <v>5.150728331898683</v>
       </c>
       <c r="D4" t="n">
-        <v>6.235134649669795</v>
+        <v>6.442173144055114</v>
       </c>
       <c r="E4" t="n">
-        <v>12.81169377253786</v>
+        <v>12.99179995206576</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.582671873581764</v>
+        <v>1.575419238366609</v>
       </c>
       <c r="C5" t="n">
-        <v>5.866725929229537</v>
+        <v>5.814074169560308</v>
       </c>
       <c r="D5" t="n">
-        <v>6.479284519442127</v>
+        <v>6.763812577712818</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92868232225343</v>
+        <v>14.15330598563973</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.779354826838336</v>
+        <v>1.780594859376541</v>
       </c>
       <c r="C6" t="n">
-        <v>6.702012874266546</v>
+        <v>6.648436770972221</v>
       </c>
       <c r="D6" t="n">
-        <v>6.799845531576416</v>
+        <v>7.269384999311181</v>
       </c>
       <c r="E6" t="n">
-        <v>15.2812132326813</v>
+        <v>15.69841662965994</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.994675140772877</v>
+        <v>2.005503642896279</v>
       </c>
       <c r="C7" t="n">
-        <v>7.672100239348088</v>
+        <v>7.605198133769822</v>
       </c>
       <c r="D7" t="n">
-        <v>7.187625303230602</v>
+        <v>7.68613852401008</v>
       </c>
       <c r="E7" t="n">
-        <v>16.85440068335157</v>
+        <v>17.29684030067618</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.213903682561419</v>
+        <v>1.20508627202272</v>
       </c>
       <c r="C8" t="n">
-        <v>5.350226822557421</v>
+        <v>5.28121602776929</v>
       </c>
       <c r="D8" t="n">
-        <v>5.427743473471914</v>
+        <v>5.991160032898353</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99187397859076</v>
+        <v>12.47746233269036</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.523100227117996</v>
+        <v>1.494139997079605</v>
       </c>
       <c r="C9" t="n">
-        <v>6.628375604909048</v>
+        <v>6.512739495431505</v>
       </c>
       <c r="D9" t="n">
-        <v>5.974921444474854</v>
+        <v>6.540838981694865</v>
       </c>
       <c r="E9" t="n">
-        <v>14.1263972765019</v>
+        <v>14.54771847420597</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850230348576745</v>
+        <v>1.793231490432892</v>
       </c>
       <c r="C10" t="n">
-        <v>8.12644893589405</v>
+        <v>7.881354446956808</v>
       </c>
       <c r="D10" t="n">
-        <v>6.512353846503999</v>
+        <v>7.139885864968166</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48903313097479</v>
+        <v>16.81447180235786</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.186765058736039</v>
+        <v>2.087629240834333</v>
       </c>
       <c r="C11" t="n">
-        <v>9.802203334398461</v>
+        <v>9.399737661399763</v>
       </c>
       <c r="D11" t="n">
-        <v>7.014492287202731</v>
+        <v>7.687262891455036</v>
       </c>
       <c r="E11" t="n">
-        <v>19.00346068033723</v>
+        <v>19.17462979368913</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.510841207555312</v>
+        <v>2.376885808885378</v>
       </c>
       <c r="C12" t="n">
-        <v>11.56016176923857</v>
+        <v>11.00789748269338</v>
       </c>
       <c r="D12" t="n">
-        <v>7.506526214594225</v>
+        <v>8.207324172856554</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5775291913881</v>
+        <v>21.59210746443531</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.812276407568979</v>
+        <v>2.654421017361851</v>
       </c>
       <c r="C13" t="n">
-        <v>13.37632273746454</v>
+        <v>12.62997227834434</v>
       </c>
       <c r="D13" t="n">
-        <v>8.042416262124863</v>
+        <v>8.728823205780403</v>
       </c>
       <c r="E13" t="n">
-        <v>24.23101540715839</v>
+        <v>24.01321650148659</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.61221626243707</v>
+        <v>1.535855926000753</v>
       </c>
       <c r="C14" t="n">
-        <v>9.364665548838348</v>
+        <v>8.847873557322826</v>
       </c>
       <c r="D14" t="n">
-        <v>6.153653515081261</v>
+        <v>6.594792028507523</v>
       </c>
       <c r="E14" t="n">
-        <v>17.13053532635668</v>
+        <v>16.9785215118311</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.636887582244792</v>
+        <v>1.550984658123196</v>
       </c>
       <c r="C15" t="n">
-        <v>10.26347520703039</v>
+        <v>9.570950376454688</v>
       </c>
       <c r="D15" t="n">
-        <v>6.18832884399526</v>
+        <v>6.6361432418104</v>
       </c>
       <c r="E15" t="n">
-        <v>18.08869163327044</v>
+        <v>17.75807827638828</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.877307777537793</v>
+        <v>1.790629272729842</v>
       </c>
       <c r="C16" t="n">
-        <v>12.20788544015345</v>
+        <v>11.2764326707952</v>
       </c>
       <c r="D16" t="n">
-        <v>6.654374296678264</v>
+        <v>7.20937590884307</v>
       </c>
       <c r="E16" t="n">
-        <v>20.7395675143695</v>
+        <v>20.27643785236812</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.490656261697229</v>
+        <v>1.429984253574777</v>
       </c>
       <c r="C17" t="n">
-        <v>11.30484444935611</v>
+        <v>10.35135144403752</v>
       </c>
       <c r="D17" t="n">
-        <v>6.190606498669113</v>
+        <v>6.728407891055515</v>
       </c>
       <c r="E17" t="n">
-        <v>18.98610720972245</v>
+        <v>18.50974358866781</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.678386057703305</v>
+        <v>1.621415238425862</v>
       </c>
       <c r="C18" t="n">
-        <v>13.18171044042699</v>
+        <v>12.07202137536274</v>
       </c>
       <c r="D18" t="n">
-        <v>6.582716531745289</v>
+        <v>7.230679834025227</v>
       </c>
       <c r="E18" t="n">
-        <v>21.44281302987558</v>
+        <v>20.92411644781383</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.664612137412722</v>
+        <v>1.618047843800296</v>
       </c>
       <c r="C19" t="n">
-        <v>14.09132914084278</v>
+        <v>12.90561353356166</v>
       </c>
       <c r="D19" t="n">
-        <v>6.661442880148839</v>
+        <v>7.353555376688756</v>
       </c>
       <c r="E19" t="n">
-        <v>22.41738415840435</v>
+        <v>21.87721675405071</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.831892128739336</v>
+        <v>1.791728830158599</v>
       </c>
       <c r="C20" t="n">
-        <v>16.06182441046769</v>
+        <v>14.79573311863987</v>
       </c>
       <c r="D20" t="n">
-        <v>7.076584714366647</v>
+        <v>7.812100276911314</v>
       </c>
       <c r="E20" t="n">
-        <v>24.97030125357367</v>
+        <v>24.39956222570979</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.07812587637272</v>
+        <v>1.061877951867435</v>
       </c>
       <c r="C21" t="n">
-        <v>11.66603924722555</v>
+        <v>10.84218602625275</v>
       </c>
       <c r="D21" t="n">
-        <v>5.907843524891946</v>
+        <v>6.538439710283758</v>
       </c>
       <c r="E21" t="n">
-        <v>18.65200864849022</v>
+        <v>18.44250368840395</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_85_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264035939407019</v>
+        <v>2.587238516793319</v>
       </c>
       <c r="C3" t="n">
-        <v>4.644635517131666</v>
+        <v>7.726773753291729</v>
       </c>
       <c r="D3" t="n">
-        <v>6.156377958895187</v>
+        <v>8.142603446603424</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06504941543387</v>
+        <v>18.45661571668847</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.398898476111962</v>
+        <v>1.059752201947111</v>
       </c>
       <c r="C4" t="n">
-        <v>5.150728331898683</v>
+        <v>4.551092029625361</v>
       </c>
       <c r="D4" t="n">
-        <v>6.442173144055114</v>
+        <v>5.660806659578847</v>
       </c>
       <c r="E4" t="n">
-        <v>12.99179995206576</v>
+        <v>11.27165089115132</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.575419238366609</v>
+        <v>1.138741242083255</v>
       </c>
       <c r="C5" t="n">
-        <v>5.814074169560308</v>
+        <v>5.262709504873431</v>
       </c>
       <c r="D5" t="n">
-        <v>6.763812577712818</v>
+        <v>5.923840503655302</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15330598563973</v>
+        <v>12.32529125061199</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.780594859376541</v>
+        <v>1.221324191624485</v>
       </c>
       <c r="C6" t="n">
-        <v>6.648436770972221</v>
+        <v>6.211532137615981</v>
       </c>
       <c r="D6" t="n">
-        <v>7.269384999311181</v>
+        <v>6.248606615974894</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69841662965994</v>
+        <v>13.68146294521536</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.005503642896279</v>
+        <v>1.305161069048748</v>
       </c>
       <c r="C7" t="n">
-        <v>7.605198133769822</v>
+        <v>7.384667880906196</v>
       </c>
       <c r="D7" t="n">
-        <v>7.68613852401008</v>
+        <v>6.669292965440993</v>
       </c>
       <c r="E7" t="n">
-        <v>17.29684030067618</v>
+        <v>15.35912191539594</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.20508627202272</v>
+        <v>1.401516456613782</v>
       </c>
       <c r="C8" t="n">
-        <v>5.28121602776929</v>
+        <v>8.717219678491697</v>
       </c>
       <c r="D8" t="n">
-        <v>5.991160032898353</v>
+        <v>7.037519240460947</v>
       </c>
       <c r="E8" t="n">
-        <v>12.47746233269036</v>
+        <v>17.15625537556642</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.494139997079605</v>
+        <v>1.484456528260678</v>
       </c>
       <c r="C9" t="n">
-        <v>6.512739495431505</v>
+        <v>10.17987082376067</v>
       </c>
       <c r="D9" t="n">
-        <v>6.540838981694865</v>
+        <v>7.400989008888023</v>
       </c>
       <c r="E9" t="n">
-        <v>14.54771847420597</v>
+        <v>19.06531636090937</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.793231490432892</v>
+        <v>0.9519418439458772</v>
       </c>
       <c r="C10" t="n">
-        <v>7.881354446956808</v>
+        <v>7.404596439832548</v>
       </c>
       <c r="D10" t="n">
-        <v>7.139885864968166</v>
+        <v>5.851687556209029</v>
       </c>
       <c r="E10" t="n">
-        <v>16.81447180235786</v>
+        <v>14.20822583998745</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.087629240834333</v>
+        <v>0.86949467174323</v>
       </c>
       <c r="C11" t="n">
-        <v>9.399737661399763</v>
+        <v>7.989354824913075</v>
       </c>
       <c r="D11" t="n">
-        <v>7.687262891455036</v>
+        <v>5.694480296327987</v>
       </c>
       <c r="E11" t="n">
-        <v>19.17462979368913</v>
+        <v>14.55332979298429</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.376885808885378</v>
+        <v>0.9230784614410209</v>
       </c>
       <c r="C12" t="n">
-        <v>11.00789748269338</v>
+        <v>9.58536243275303</v>
       </c>
       <c r="D12" t="n">
-        <v>8.207324172856554</v>
+        <v>6.086305622569931</v>
       </c>
       <c r="E12" t="n">
-        <v>21.59210746443531</v>
+        <v>16.59474651676398</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.654421017361851</v>
+        <v>0.7232928036267952</v>
       </c>
       <c r="C13" t="n">
-        <v>12.62997227834434</v>
+        <v>9.238815310630949</v>
       </c>
       <c r="D13" t="n">
-        <v>8.728823205780403</v>
+        <v>5.540866233044488</v>
       </c>
       <c r="E13" t="n">
-        <v>24.01321650148659</v>
+        <v>15.50297434730223</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.535855926000753</v>
+        <v>0.772743435489707</v>
       </c>
       <c r="C14" t="n">
-        <v>8.847873557322826</v>
+        <v>10.95797335049163</v>
       </c>
       <c r="D14" t="n">
-        <v>6.594792028507523</v>
+        <v>5.881267614537985</v>
       </c>
       <c r="E14" t="n">
-        <v>16.9785215118311</v>
+        <v>17.61198440051932</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.550984658123196</v>
+        <v>0.7383822658410686</v>
       </c>
       <c r="C15" t="n">
-        <v>9.570950376454688</v>
+        <v>11.96273322092598</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6361432418104</v>
+        <v>5.922000326787185</v>
       </c>
       <c r="E15" t="n">
-        <v>17.75807827638828</v>
+        <v>18.62311581355423</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.790629272729842</v>
+        <v>0.7956083395216152</v>
       </c>
       <c r="C16" t="n">
-        <v>11.2764326707952</v>
+        <v>13.98975752336141</v>
       </c>
       <c r="D16" t="n">
-        <v>7.20937590884307</v>
+        <v>6.31076260019188</v>
       </c>
       <c r="E16" t="n">
-        <v>20.27643785236812</v>
+        <v>21.0961284630749</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.429984253574777</v>
+        <v>0.4766974152740813</v>
       </c>
       <c r="C17" t="n">
-        <v>10.35135144403752</v>
+        <v>10.48174717411558</v>
       </c>
       <c r="D17" t="n">
-        <v>6.728407891055515</v>
+        <v>5.234207520145954</v>
       </c>
       <c r="E17" t="n">
-        <v>18.50974358866781</v>
+        <v>16.19265210953562</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.621415238425862</v>
+        <v>0.3671834588653496</v>
       </c>
       <c r="C18" t="n">
-        <v>12.07202137536274</v>
+        <v>9.434664160151147</v>
       </c>
       <c r="D18" t="n">
-        <v>7.230679834025227</v>
+        <v>4.750873490391165</v>
       </c>
       <c r="E18" t="n">
-        <v>20.92411644781383</v>
+        <v>14.55272110940766</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.618047843800296</v>
+        <v>0.421974798239364</v>
       </c>
       <c r="C19" t="n">
-        <v>12.90561353356166</v>
+        <v>11.68587055085134</v>
       </c>
       <c r="D19" t="n">
-        <v>7.353555376688756</v>
+        <v>5.193091926292099</v>
       </c>
       <c r="E19" t="n">
-        <v>21.87721675405071</v>
+        <v>17.3009372753828</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.791728830158599</v>
+        <v>0.4725053525769474</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79573311863987</v>
+        <v>13.99616833587014</v>
       </c>
       <c r="D20" t="n">
-        <v>7.812100276911314</v>
+        <v>5.622950158596565</v>
       </c>
       <c r="E20" t="n">
-        <v>24.39956222570979</v>
+        <v>20.09162384704365</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.061877951867435</v>
+        <v>0.5190009238500763</v>
       </c>
       <c r="C21" t="n">
-        <v>10.84218602625275</v>
+        <v>16.41609788702219</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538439710283758</v>
+        <v>6.052121167508057</v>
       </c>
       <c r="E21" t="n">
-        <v>18.44250368840395</v>
+        <v>22.98721997838032</v>
       </c>
     </row>
   </sheetData>
